--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/20.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/20.xlsx
@@ -426,13 +426,13 @@
         <v>-13.097233004737</v>
       </c>
       <c r="E2">
-        <v>-13.53332484772052</v>
+        <v>-14.78672664665185</v>
       </c>
       <c r="F2">
-        <v>1.873428115617229</v>
+        <v>-0.3225862947153024</v>
       </c>
       <c r="G2">
-        <v>-17.69302207666713</v>
+        <v>-19.05935134230938</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.53764792868274</v>
       </c>
       <c r="E3">
-        <v>-14.35328920637009</v>
+        <v>-14.8248905055157</v>
       </c>
       <c r="F3">
-        <v>1.850382934471347</v>
+        <v>-0.1651119947083108</v>
       </c>
       <c r="G3">
-        <v>-16.69678282665503</v>
+        <v>-18.28957199424734</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.78307977265208</v>
       </c>
       <c r="E4">
-        <v>-13.504115312473</v>
+        <v>-15.376079793279</v>
       </c>
       <c r="F4">
-        <v>2.278607463348551</v>
+        <v>-0.01302125445211318</v>
       </c>
       <c r="G4">
-        <v>-17.00076226237672</v>
+        <v>-18.03790404789779</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.91926514215135</v>
       </c>
       <c r="E5">
-        <v>-13.80364906643096</v>
+        <v>-15.75324537332065</v>
       </c>
       <c r="F5">
-        <v>2.385905893033171</v>
+        <v>-0.05134650071003511</v>
       </c>
       <c r="G5">
-        <v>-16.18326894616748</v>
+        <v>-17.50575728326346</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.983658530357504</v>
       </c>
       <c r="E6">
-        <v>-13.88489003315593</v>
+        <v>-14.77474878519105</v>
       </c>
       <c r="F6">
-        <v>1.73451918584178</v>
+        <v>0.4537919415171034</v>
       </c>
       <c r="G6">
-        <v>-15.25119788208806</v>
+        <v>-17.03620573094567</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.028813008573442</v>
       </c>
       <c r="E7">
-        <v>-15.45206279446673</v>
+        <v>-17.95455535897422</v>
       </c>
       <c r="F7">
-        <v>1.715231479234996</v>
+        <v>0.03162940529358577</v>
       </c>
       <c r="G7">
-        <v>-15.39989153490262</v>
+        <v>-16.63301669538939</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.09907199627318</v>
       </c>
       <c r="E8">
-        <v>-15.84543005188655</v>
+        <v>-17.03663751122857</v>
       </c>
       <c r="F8">
-        <v>1.838898448798934</v>
+        <v>0.2451891486745207</v>
       </c>
       <c r="G8">
-        <v>-13.57649138146039</v>
+        <v>-16.35435234459543</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.226135294221971</v>
       </c>
       <c r="E9">
-        <v>-15.53425899979642</v>
+        <v>-18.93121622769825</v>
       </c>
       <c r="F9">
-        <v>2.629689449472649</v>
+        <v>0.3174509506903328</v>
       </c>
       <c r="G9">
-        <v>-13.34335450021857</v>
+        <v>-15.4368844803864</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.440281578714137</v>
       </c>
       <c r="E10">
-        <v>-17.36900655392062</v>
+        <v>-19.09546742917257</v>
       </c>
       <c r="F10">
-        <v>2.727362249936739</v>
+        <v>0.687073456023889</v>
       </c>
       <c r="G10">
-        <v>-13.23765458933046</v>
+        <v>-14.99200446445463</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.751091609407958</v>
       </c>
       <c r="E11">
-        <v>-16.25699668133175</v>
+        <v>-19.84485626777933</v>
       </c>
       <c r="F11">
-        <v>2.491234465033934</v>
+        <v>1.100225011639754</v>
       </c>
       <c r="G11">
-        <v>-12.64617082162931</v>
+        <v>-14.62344434515487</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.175539121771384</v>
       </c>
       <c r="E12">
-        <v>-18.842300126445</v>
+        <v>-20.1558155060919</v>
       </c>
       <c r="F12">
-        <v>2.894743824081212</v>
+        <v>0.8571107760617379</v>
       </c>
       <c r="G12">
-        <v>-11.82896729806969</v>
+        <v>-13.71679018504223</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.705535493877964</v>
       </c>
       <c r="E13">
-        <v>-18.01412902221756</v>
+        <v>-20.28809528678769</v>
       </c>
       <c r="F13">
-        <v>2.865147913513991</v>
+        <v>1.433921222713895</v>
       </c>
       <c r="G13">
-        <v>-11.69616916369812</v>
+        <v>-13.44570743654087</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.344457603824535</v>
       </c>
       <c r="E14">
-        <v>-20.14986810747474</v>
+        <v>-20.67943993029231</v>
       </c>
       <c r="F14">
-        <v>3.420173954207328</v>
+        <v>1.847871324506059</v>
       </c>
       <c r="G14">
-        <v>-10.55616926277637</v>
+        <v>-13.42313363343381</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.067900167204687</v>
       </c>
       <c r="E15">
-        <v>-20.72703988528617</v>
+        <v>-22.01124605261375</v>
       </c>
       <c r="F15">
-        <v>3.684250855280587</v>
+        <v>1.837246684197752</v>
       </c>
       <c r="G15">
-        <v>-11.29614435058627</v>
+        <v>-13.17143305277687</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.86203897386851</v>
       </c>
       <c r="E16">
-        <v>-21.20494160601154</v>
+        <v>-22.41046933800157</v>
       </c>
       <c r="F16">
-        <v>4.110159268899564</v>
+        <v>2.007240929130655</v>
       </c>
       <c r="G16">
-        <v>-9.819349259804829</v>
+        <v>-12.94963594066655</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.69198864914895</v>
       </c>
       <c r="E17">
-        <v>-21.59938039195315</v>
+        <v>-23.3344716403381</v>
       </c>
       <c r="F17">
-        <v>3.499957332240559</v>
+        <v>2.080977225123451</v>
       </c>
       <c r="G17">
-        <v>-10.23524217854147</v>
+        <v>-12.36889799770242</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.536354726260975</v>
       </c>
       <c r="E18">
-        <v>-22.73317385794074</v>
+        <v>-24.69880986696692</v>
       </c>
       <c r="F18">
-        <v>4.338866538608091</v>
+        <v>2.3719777235225</v>
       </c>
       <c r="G18">
-        <v>-10.04091662639114</v>
+        <v>-12.75262001621507</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.365043690648466</v>
       </c>
       <c r="E19">
-        <v>-23.52059365264896</v>
+        <v>-25.14091090607227</v>
       </c>
       <c r="F19">
-        <v>4.062924102857131</v>
+        <v>2.806469680169286</v>
       </c>
       <c r="G19">
-        <v>-9.661858703090513</v>
+        <v>-12.08525495697321</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.166028102033407</v>
       </c>
       <c r="E20">
-        <v>-23.96209662932354</v>
+        <v>-25.6755454934948</v>
       </c>
       <c r="F20">
-        <v>4.548042561693411</v>
+        <v>2.566508210926325</v>
       </c>
       <c r="G20">
-        <v>-9.065598578159921</v>
+        <v>-12.32723181940055</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.925781717716728</v>
       </c>
       <c r="E21">
-        <v>-24.37267479447344</v>
+        <v>-27.31341837118816</v>
       </c>
       <c r="F21">
-        <v>5.088519157323977</v>
+        <v>3.002093612544806</v>
       </c>
       <c r="G21">
-        <v>-9.008754836177612</v>
+        <v>-11.77851204810183</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.646140133674981</v>
       </c>
       <c r="E22">
-        <v>-25.65245779174008</v>
+        <v>-26.82538281483021</v>
       </c>
       <c r="F22">
-        <v>5.254923257933147</v>
+        <v>3.019797480677437</v>
       </c>
       <c r="G22">
-        <v>-9.665444560786407</v>
+        <v>-11.54124888503376</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.327856747552235</v>
       </c>
       <c r="E23">
-        <v>-25.32315381900575</v>
+        <v>-28.22616754744006</v>
       </c>
       <c r="F23">
-        <v>4.870898756934518</v>
+        <v>2.699544015815925</v>
       </c>
       <c r="G23">
-        <v>-8.916149114786233</v>
+        <v>-11.16561103714749</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.982808869708502</v>
       </c>
       <c r="E24">
-        <v>-25.63709506304954</v>
+        <v>-27.91727868497293</v>
       </c>
       <c r="F24">
-        <v>5.299250854391754</v>
+        <v>2.997386828962099</v>
       </c>
       <c r="G24">
-        <v>-8.553341771192994</v>
+        <v>-11.12430905771608</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.619783248061514</v>
       </c>
       <c r="E25">
-        <v>-27.74927713367229</v>
+        <v>-29.48338614757891</v>
       </c>
       <c r="F25">
-        <v>5.327981949390452</v>
+        <v>3.138119823758513</v>
       </c>
       <c r="G25">
-        <v>-8.205760290055126</v>
+        <v>-11.29900572665813</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.253798561893336</v>
       </c>
       <c r="E26">
-        <v>-26.66281366394244</v>
+        <v>-28.94283115741284</v>
       </c>
       <c r="F26">
-        <v>5.559089827832292</v>
+        <v>3.15430446607441</v>
       </c>
       <c r="G26">
-        <v>-9.143573686862702</v>
+        <v>-11.01763403372319</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.8945458766277046</v>
       </c>
       <c r="E27">
-        <v>-26.87105983298067</v>
+        <v>-29.73339700969962</v>
       </c>
       <c r="F27">
-        <v>4.823812697024588</v>
+        <v>2.932578676836677</v>
       </c>
       <c r="G27">
-        <v>-8.281671605158632</v>
+        <v>-10.78373873117764</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.5545031148949118</v>
       </c>
       <c r="E28">
-        <v>-26.53634837910141</v>
+        <v>-30.86035428984654</v>
       </c>
       <c r="F28">
-        <v>4.792901339021722</v>
+        <v>2.758561879795779</v>
       </c>
       <c r="G28">
-        <v>-7.341364947266541</v>
+        <v>-10.10044812993</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.2417056087308396</v>
       </c>
       <c r="E29">
-        <v>-25.41914283914518</v>
+        <v>-29.8671470272044</v>
       </c>
       <c r="F29">
-        <v>4.584296889444334</v>
+        <v>3.236408929570285</v>
       </c>
       <c r="G29">
-        <v>-8.346034291563347</v>
+        <v>-9.957729166112198</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.0343639447212503</v>
       </c>
       <c r="E30">
-        <v>-26.94075902543394</v>
+        <v>-30.65903983050945</v>
       </c>
       <c r="F30">
-        <v>4.269573605363912</v>
+        <v>2.834562932267828</v>
       </c>
       <c r="G30">
-        <v>-8.169207255034948</v>
+        <v>-9.732754777834488</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.2683690555570722</v>
       </c>
       <c r="E31">
-        <v>-26.95384164110715</v>
+        <v>-31.02677346763242</v>
       </c>
       <c r="F31">
-        <v>4.570685156281533</v>
+        <v>3.307068669029083</v>
       </c>
       <c r="G31">
-        <v>-8.118314705348082</v>
+        <v>-9.03012247528358</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.4549019993031643</v>
       </c>
       <c r="E32">
-        <v>-26.68625438865978</v>
+        <v>-29.87674717518173</v>
       </c>
       <c r="F32">
-        <v>5.203942214495254</v>
+        <v>2.996599879929439</v>
       </c>
       <c r="G32">
-        <v>-8.267820299730479</v>
+        <v>-9.310542551815058</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.5902985015791855</v>
       </c>
       <c r="E33">
-        <v>-28.67832351116282</v>
+        <v>-30.75064513609553</v>
       </c>
       <c r="F33">
-        <v>5.170078555068811</v>
+        <v>2.89993603096196</v>
       </c>
       <c r="G33">
-        <v>-7.454410188061747</v>
+        <v>-8.98136943078913</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.6727990310209818</v>
       </c>
       <c r="E34">
-        <v>-26.47968611699678</v>
+        <v>-30.76770860482359</v>
       </c>
       <c r="F34">
-        <v>4.755339847509182</v>
+        <v>2.745102566235093</v>
       </c>
       <c r="G34">
-        <v>-8.038515991548408</v>
+        <v>-8.458575658652467</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.7026710004594313</v>
       </c>
       <c r="E35">
-        <v>-25.93117149732667</v>
+        <v>-29.72692007663855</v>
       </c>
       <c r="F35">
-        <v>4.63561922025218</v>
+        <v>2.994671440615722</v>
       </c>
       <c r="G35">
-        <v>-7.428529876930041</v>
+        <v>-8.557539848495503</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.6835818187166929</v>
       </c>
       <c r="E36">
-        <v>-27.8471683245985</v>
+        <v>-29.51247316309235</v>
       </c>
       <c r="F36">
-        <v>4.376209341126293</v>
+        <v>3.102135543780902</v>
       </c>
       <c r="G36">
-        <v>-7.505619943216434</v>
+        <v>-7.887817286887872</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.6210350394449369</v>
       </c>
       <c r="E37">
-        <v>-25.07008204013865</v>
+        <v>-29.84864239414662</v>
       </c>
       <c r="F37">
-        <v>5.201985610689841</v>
+        <v>3.043255188789913</v>
       </c>
       <c r="G37">
-        <v>-8.140459040969905</v>
+        <v>-7.871147682673614</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.5234922114166765</v>
       </c>
       <c r="E38">
-        <v>-25.50199109865287</v>
+        <v>-29.70987529736145</v>
       </c>
       <c r="F38">
-        <v>4.788925175488285</v>
+        <v>2.980249564132983</v>
       </c>
       <c r="G38">
-        <v>-7.554057087615359</v>
+        <v>-7.872533988051495</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.3987355890581007</v>
       </c>
       <c r="E39">
-        <v>-25.12176044865349</v>
+        <v>-29.37704940142367</v>
       </c>
       <c r="F39">
-        <v>4.923090873515304</v>
+        <v>3.365453660313197</v>
       </c>
       <c r="G39">
-        <v>-8.120296260492736</v>
+        <v>-7.660947498037014</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.253808444943567</v>
       </c>
       <c r="E40">
-        <v>-25.04000448372424</v>
+        <v>-28.71310665600826</v>
       </c>
       <c r="F40">
-        <v>5.09885883924572</v>
+        <v>3.198128415152115</v>
       </c>
       <c r="G40">
-        <v>-7.419368774159824</v>
+        <v>-8.020074997129081</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.09414615133908516</v>
       </c>
       <c r="E41">
-        <v>-24.52216548289931</v>
+        <v>-28.8076316691557</v>
       </c>
       <c r="F41">
-        <v>4.866611127257628</v>
+        <v>3.468638417475515</v>
       </c>
       <c r="G41">
-        <v>-8.177988494467158</v>
+        <v>-7.767354920709314</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.07659549984750499</v>
       </c>
       <c r="E42">
-        <v>-24.92284239225082</v>
+        <v>-29.28279642361801</v>
       </c>
       <c r="F42">
-        <v>4.998594905545674</v>
+        <v>3.621036482038152</v>
       </c>
       <c r="G42">
-        <v>-7.339479989671758</v>
+        <v>-8.372701742189275</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.25557823697406</v>
       </c>
       <c r="E43">
-        <v>-24.77517496359654</v>
+        <v>-27.69308418444736</v>
       </c>
       <c r="F43">
-        <v>4.944618485579258</v>
+        <v>3.466852457355079</v>
       </c>
       <c r="G43">
-        <v>-8.055152961455278</v>
+        <v>-8.435300870622692</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.4427137029254759</v>
       </c>
       <c r="E44">
-        <v>-23.5142433925333</v>
+        <v>-28.14043903587861</v>
       </c>
       <c r="F44">
-        <v>5.187374866439264</v>
+        <v>3.749208113538514</v>
       </c>
       <c r="G44">
-        <v>-7.936943667858851</v>
+        <v>-8.403410625442243</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.6364914615405382</v>
       </c>
       <c r="E45">
-        <v>-22.88001064433006</v>
+        <v>-27.8550801921723</v>
       </c>
       <c r="F45">
-        <v>5.000433881179888</v>
+        <v>3.697736676598163</v>
       </c>
       <c r="G45">
-        <v>-7.361527727743709</v>
+        <v>-8.196412519046644</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.8382505701918126</v>
       </c>
       <c r="E46">
-        <v>-23.04736844787535</v>
+        <v>-26.70437484967</v>
       </c>
       <c r="F46">
-        <v>4.874596589020616</v>
+        <v>3.767723781725888</v>
       </c>
       <c r="G46">
-        <v>-8.051543607058065</v>
+        <v>-8.90867063690499</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.046373415479528</v>
       </c>
       <c r="E47">
-        <v>-22.015353578614</v>
+        <v>-26.04759847039559</v>
       </c>
       <c r="F47">
-        <v>5.020135771488071</v>
+        <v>3.845464405743816</v>
       </c>
       <c r="G47">
-        <v>-6.901363107603264</v>
+        <v>-8.848982488690661</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.263242038652549</v>
       </c>
       <c r="E48">
-        <v>-22.4531975761114</v>
+        <v>-26.29643812692269</v>
       </c>
       <c r="F48">
-        <v>4.683550214912965</v>
+        <v>3.480487384805159</v>
       </c>
       <c r="G48">
-        <v>-8.015648479674848</v>
+        <v>-9.459349772019332</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.486678576535809</v>
       </c>
       <c r="E49">
-        <v>-21.24431820258224</v>
+        <v>-25.98330260587592</v>
       </c>
       <c r="F49">
-        <v>4.907949974126935</v>
+        <v>3.873562628046775</v>
       </c>
       <c r="G49">
-        <v>-7.988129926312218</v>
+        <v>-8.999981428979176</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.718700855479756</v>
       </c>
       <c r="E50">
-        <v>-21.28553467176983</v>
+        <v>-26.05010701003579</v>
       </c>
       <c r="F50">
-        <v>5.41610864390468</v>
+        <v>3.696818845515862</v>
       </c>
       <c r="G50">
-        <v>-8.169739846931536</v>
+        <v>-9.094507353017319</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.956181672880345</v>
       </c>
       <c r="E51">
-        <v>-20.63912886117352</v>
+        <v>-25.63339870497044</v>
       </c>
       <c r="F51">
-        <v>5.181034542338237</v>
+        <v>3.749809508272946</v>
       </c>
       <c r="G51">
-        <v>-8.408753514247957</v>
+        <v>-9.687313462853867</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.200364425948904</v>
       </c>
       <c r="E52">
-        <v>-19.90966297729196</v>
+        <v>-24.68871756344759</v>
       </c>
       <c r="F52">
-        <v>5.41243069263625</v>
+        <v>3.727483350032694</v>
       </c>
       <c r="G52">
-        <v>-8.521721738077725</v>
+        <v>-9.53178226995518</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.446586093244541</v>
       </c>
       <c r="E53">
-        <v>-21.93908400584485</v>
+        <v>-24.43423784594137</v>
       </c>
       <c r="F53">
-        <v>4.87318339423144</v>
+        <v>3.776812628869404</v>
       </c>
       <c r="G53">
-        <v>-8.488904678567431</v>
+        <v>-9.84114506102374</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.695150796744705</v>
       </c>
       <c r="E54">
-        <v>-18.71690637012578</v>
+        <v>-24.07921303547238</v>
       </c>
       <c r="F54">
-        <v>4.704401879176235</v>
+        <v>3.987451548788068</v>
       </c>
       <c r="G54">
-        <v>-9.085663455714924</v>
+        <v>-9.710200555311861</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.939856061038847</v>
       </c>
       <c r="E55">
-        <v>-18.67685280010913</v>
+        <v>-23.59870725124634</v>
       </c>
       <c r="F55">
-        <v>4.512767364212597</v>
+        <v>3.926182182207405</v>
       </c>
       <c r="G55">
-        <v>-9.724309019082238</v>
+        <v>-10.39062978048765</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.180294975952859</v>
       </c>
       <c r="E56">
-        <v>-19.54329574669486</v>
+        <v>-22.3963899516104</v>
       </c>
       <c r="F56">
-        <v>4.762574808405232</v>
+        <v>3.932744508772383</v>
       </c>
       <c r="G56">
-        <v>-9.774272143694668</v>
+        <v>-10.43870272601611</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.409542283705244</v>
       </c>
       <c r="E57">
-        <v>-19.33045197272005</v>
+        <v>-23.01565452619896</v>
       </c>
       <c r="F57">
-        <v>4.465553735722636</v>
+        <v>4.027536247409536</v>
       </c>
       <c r="G57">
-        <v>-10.33211124585014</v>
+        <v>-10.35759211305941</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.627750835001313</v>
       </c>
       <c r="E58">
-        <v>-18.41906712638835</v>
+        <v>-22.49288151032014</v>
       </c>
       <c r="F58">
-        <v>4.611266875344681</v>
+        <v>4.209210472721913</v>
       </c>
       <c r="G58">
-        <v>-8.987610415734187</v>
+        <v>-10.65513084187481</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.828755809772839</v>
       </c>
       <c r="E59">
-        <v>-18.81429917569301</v>
+        <v>-22.14561905181725</v>
       </c>
       <c r="F59">
-        <v>4.558887547730862</v>
+        <v>4.241364381828978</v>
       </c>
       <c r="G59">
-        <v>-9.481944461083122</v>
+        <v>-10.28389340399687</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.014731398593204</v>
       </c>
       <c r="E60">
-        <v>-19.27476571527675</v>
+        <v>-22.66177600205562</v>
       </c>
       <c r="F60">
-        <v>5.077235136563042</v>
+        <v>4.32604506794756</v>
       </c>
       <c r="G60">
-        <v>-10.15865598596116</v>
+        <v>-10.99682770470431</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.181210994227566</v>
       </c>
       <c r="E61">
-        <v>-17.82619620976907</v>
+        <v>-21.95208771050289</v>
       </c>
       <c r="F61">
-        <v>4.970282964452791</v>
+        <v>4.504540019167992</v>
       </c>
       <c r="G61">
-        <v>-9.50288002195926</v>
+        <v>-11.08215467017567</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.332324706603146</v>
       </c>
       <c r="E62">
-        <v>-17.35028803047962</v>
+        <v>-21.99897746636021</v>
       </c>
       <c r="F62">
-        <v>4.687011133921862</v>
+        <v>4.404816181014571</v>
       </c>
       <c r="G62">
-        <v>-9.898033185664097</v>
+        <v>-11.56932874848347</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.466559824185197</v>
       </c>
       <c r="E63">
-        <v>-16.25251536631226</v>
+        <v>-20.78211146745339</v>
       </c>
       <c r="F63">
-        <v>5.018856772218149</v>
+        <v>4.368013474042995</v>
       </c>
       <c r="G63">
-        <v>-10.54939568593472</v>
+        <v>-11.59545838572363</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.589872565744964</v>
       </c>
       <c r="E64">
-        <v>-16.69125645745583</v>
+        <v>-21.25370861338767</v>
       </c>
       <c r="F64">
-        <v>4.404632283451149</v>
+        <v>4.11432430020084</v>
       </c>
       <c r="G64">
-        <v>-11.19000844535144</v>
+        <v>-11.86997034724542</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.702760659890952</v>
       </c>
       <c r="E65">
-        <v>-15.92777577282392</v>
+        <v>-20.4410040681339</v>
       </c>
       <c r="F65">
-        <v>5.267320604483444</v>
+        <v>4.148728055173909</v>
       </c>
       <c r="G65">
-        <v>-10.10663689998323</v>
+        <v>-11.81634043185477</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.811005704248807</v>
       </c>
       <c r="E66">
-        <v>-16.7493640371015</v>
+        <v>-21.32498602614438</v>
       </c>
       <c r="F66">
-        <v>4.603296324194944</v>
+        <v>4.702586097829298</v>
       </c>
       <c r="G66">
-        <v>-10.04654930784646</v>
+        <v>-12.70494651460904</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.914910620880413</v>
       </c>
       <c r="E67">
-        <v>-17.78353442304043</v>
+        <v>-21.59084969589195</v>
       </c>
       <c r="F67">
-        <v>5.078754362379776</v>
+        <v>4.239300090261202</v>
       </c>
       <c r="G67">
-        <v>-10.20498625947506</v>
+        <v>-12.30078236594798</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.018850602833725</v>
       </c>
       <c r="E68">
-        <v>-16.51052116023326</v>
+        <v>-21.06807252680181</v>
       </c>
       <c r="F68">
-        <v>4.214868222083033</v>
+        <v>4.437099315436473</v>
       </c>
       <c r="G68">
-        <v>-10.7975312948525</v>
+        <v>-12.73425212264429</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.123273908701008</v>
       </c>
       <c r="E69">
-        <v>-15.0846032692912</v>
+        <v>-21.03475131234271</v>
       </c>
       <c r="F69">
-        <v>4.875663526235421</v>
+        <v>4.78006164427833</v>
       </c>
       <c r="G69">
-        <v>-11.07517092839444</v>
+        <v>-12.59082173092541</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.232296132711668</v>
       </c>
       <c r="E70">
-        <v>-17.55033991357396</v>
+        <v>-20.72181514543953</v>
       </c>
       <c r="F70">
-        <v>5.086320670236947</v>
+        <v>4.633321329076814</v>
       </c>
       <c r="G70">
-        <v>-10.33719828168592</v>
+        <v>-12.83722641617928</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.345925703421027</v>
       </c>
       <c r="E71">
-        <v>-16.41424972172374</v>
+        <v>-20.45663675556055</v>
       </c>
       <c r="F71">
-        <v>4.749031001369461</v>
+        <v>4.690402470068923</v>
       </c>
       <c r="G71">
-        <v>-10.63015254299934</v>
+        <v>-13.64783780964634</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.466283357031462</v>
       </c>
       <c r="E72">
-        <v>-17.83107207986442</v>
+        <v>-20.51842408044003</v>
       </c>
       <c r="F72">
-        <v>5.094915810408394</v>
+        <v>4.165934902864861</v>
       </c>
       <c r="G72">
-        <v>-11.16636945845121</v>
+        <v>-13.52000531148706</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.590780852787531</v>
       </c>
       <c r="E73">
-        <v>-18.3595931402168</v>
+        <v>-20.70246948708848</v>
       </c>
       <c r="F73">
-        <v>4.517195816347964</v>
+        <v>4.864299982203818</v>
       </c>
       <c r="G73">
-        <v>-10.47714724549255</v>
+        <v>-13.4246034826386</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.71918988042349</v>
       </c>
       <c r="E74">
-        <v>-17.2866525265606</v>
+        <v>-20.24555394318747</v>
       </c>
       <c r="F74">
-        <v>4.849306532213147</v>
+        <v>4.592502696936466</v>
       </c>
       <c r="G74">
-        <v>-11.3338852743954</v>
+        <v>-13.64392169275967</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.84772554767174</v>
       </c>
       <c r="E75">
-        <v>-17.48465272326047</v>
+        <v>-20.53210475854401</v>
       </c>
       <c r="F75">
-        <v>4.363088001465949</v>
+        <v>4.810494205922378</v>
       </c>
       <c r="G75">
-        <v>-9.985346927769291</v>
+        <v>-13.83596153802048</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.974893680572649</v>
       </c>
       <c r="E76">
-        <v>-18.68926259554772</v>
+        <v>-20.95433683467138</v>
       </c>
       <c r="F76">
-        <v>4.878889188901923</v>
+        <v>4.860345356222853</v>
       </c>
       <c r="G76">
-        <v>-11.25243004315267</v>
+        <v>-14.16174330182255</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.09580176175261</v>
       </c>
       <c r="E77">
-        <v>-18.6304282039202</v>
+        <v>-21.67783040066784</v>
       </c>
       <c r="F77">
-        <v>4.318926078487902</v>
+        <v>4.862779099652277</v>
       </c>
       <c r="G77">
-        <v>-10.963250918518</v>
+        <v>-13.50775830861015</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.209286136150674</v>
       </c>
       <c r="E78">
-        <v>-18.60048770347951</v>
+        <v>-22.12540537229931</v>
       </c>
       <c r="F78">
-        <v>4.492030014650914</v>
+        <v>4.490348428823231</v>
       </c>
       <c r="G78">
-        <v>-10.39215837144575</v>
+        <v>-13.38156796879869</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.312415887182689</v>
       </c>
       <c r="E79">
-        <v>-17.98336203272324</v>
+        <v>-21.45391416530103</v>
       </c>
       <c r="F79">
-        <v>4.700480387891382</v>
+        <v>4.732341054937856</v>
       </c>
       <c r="G79">
-        <v>-9.334929517040646</v>
+        <v>-13.61364097161964</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.406722970871392</v>
       </c>
       <c r="E80">
-        <v>-19.24561017177645</v>
+        <v>-22.26582960040309</v>
       </c>
       <c r="F80">
-        <v>4.580781298186853</v>
+        <v>4.497768944017509</v>
       </c>
       <c r="G80">
-        <v>-10.57732021008127</v>
+        <v>-13.48706554698099</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.490538600535676</v>
       </c>
       <c r="E81">
-        <v>-19.56541159699957</v>
+        <v>-22.03736975184692</v>
       </c>
       <c r="F81">
-        <v>5.360657729961281</v>
+        <v>4.688490598103262</v>
       </c>
       <c r="G81">
-        <v>-10.9385141135172</v>
+        <v>-13.49271258753157</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.565162682050705</v>
       </c>
       <c r="E82">
-        <v>-20.6740033766681</v>
+        <v>-23.3010507488072</v>
       </c>
       <c r="F82">
-        <v>4.501446895285939</v>
+        <v>4.727659122377234</v>
       </c>
       <c r="G82">
-        <v>-10.77160137957356</v>
+        <v>-13.25456829816399</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.629201129701378</v>
       </c>
       <c r="E83">
-        <v>-20.97818872730987</v>
+        <v>-23.94990695408517</v>
       </c>
       <c r="F83">
-        <v>4.417579665956906</v>
+        <v>5.209889892447355</v>
       </c>
       <c r="G83">
-        <v>-10.1070572298624</v>
+        <v>-13.29312899577473</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.683026044687101</v>
       </c>
       <c r="E84">
-        <v>-23.22341061630086</v>
+        <v>-25.31873895536745</v>
       </c>
       <c r="F84">
-        <v>5.036756135057841</v>
+        <v>4.609237375207822</v>
       </c>
       <c r="G84">
-        <v>-9.742257888146142</v>
+        <v>-12.84216333420107</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.725261695133441</v>
       </c>
       <c r="E85">
-        <v>-22.25648487492223</v>
+        <v>-26.33184840667818</v>
       </c>
       <c r="F85">
-        <v>4.908009616579936</v>
+        <v>4.983914578433261</v>
       </c>
       <c r="G85">
-        <v>-10.38657529413765</v>
+        <v>-13.35107838809138</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.755472609996918</v>
       </c>
       <c r="E86">
-        <v>-25.06499850947706</v>
+        <v>-26.49910653315168</v>
       </c>
       <c r="F86">
-        <v>4.629580421885772</v>
+        <v>5.582295712254317</v>
       </c>
       <c r="G86">
-        <v>-9.63914130903094</v>
+        <v>-12.87219081311576</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.771954972583468</v>
       </c>
       <c r="E87">
-        <v>-25.76623501598376</v>
+        <v>-28.31959195958642</v>
       </c>
       <c r="F87">
-        <v>5.12170521221493</v>
+        <v>5.039965230376287</v>
       </c>
       <c r="G87">
-        <v>-10.15274264946229</v>
+        <v>-12.76913167038157</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.77281506795233</v>
       </c>
       <c r="E88">
-        <v>-26.66977859933418</v>
+        <v>-29.35578703604621</v>
       </c>
       <c r="F88">
-        <v>5.148222909513348</v>
+        <v>5.73782334886473</v>
       </c>
       <c r="G88">
-        <v>-9.810086337995561</v>
+        <v>-12.93468681713783</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.75414169076921</v>
       </c>
       <c r="E89">
-        <v>-27.59981967093701</v>
+        <v>-30.78364032346563</v>
       </c>
       <c r="F89">
-        <v>4.845225994386956</v>
+        <v>5.742834971651667</v>
       </c>
       <c r="G89">
-        <v>-9.291523277468796</v>
+        <v>-12.91670661913883</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.711003060411549</v>
       </c>
       <c r="E90">
-        <v>-30.89515612414294</v>
+        <v>-31.51335955323801</v>
       </c>
       <c r="F90">
-        <v>5.33437860247487</v>
+        <v>5.840292396591028</v>
       </c>
       <c r="G90">
-        <v>-8.964103271435802</v>
+        <v>-12.4173782193871</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.636857966950857</v>
       </c>
       <c r="E91">
-        <v>-30.56746359740265</v>
+        <v>-33.14462467171357</v>
       </c>
       <c r="F91">
-        <v>4.887784198073184</v>
+        <v>5.676100036947333</v>
       </c>
       <c r="G91">
-        <v>-8.307634154744957</v>
+        <v>-11.75832316017876</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.525303954314673</v>
       </c>
       <c r="E92">
-        <v>-33.15334226228438</v>
+        <v>-34.92532648686777</v>
       </c>
       <c r="F92">
-        <v>4.597002388668473</v>
+        <v>5.645677415712118</v>
       </c>
       <c r="G92">
-        <v>-9.322890068358728</v>
+        <v>-12.21981534394378</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.37089443674456</v>
       </c>
       <c r="E93">
-        <v>-35.23587248065352</v>
+        <v>-36.88750287086037</v>
       </c>
       <c r="F93">
-        <v>5.534174193090888</v>
+        <v>6.390725968403244</v>
       </c>
       <c r="G93">
-        <v>-9.084753611224921</v>
+        <v>-12.19804434479849</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.169895003553689</v>
       </c>
       <c r="E94">
-        <v>-36.20988983036929</v>
+        <v>-39.08755651008818</v>
       </c>
       <c r="F94">
-        <v>4.740303322413565</v>
+        <v>6.065059950931841</v>
       </c>
       <c r="G94">
-        <v>-9.121951500159103</v>
+        <v>-11.88061435294339</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.922188117910294</v>
       </c>
       <c r="E95">
-        <v>-38.15532254290584</v>
+        <v>-41.13543025655729</v>
       </c>
       <c r="F95">
-        <v>5.239689581395664</v>
+        <v>5.852603592931435</v>
       </c>
       <c r="G95">
-        <v>-8.294614371469075</v>
+        <v>-11.77259479548608</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.627905841144358</v>
       </c>
       <c r="E96">
-        <v>-41.91799494722678</v>
+        <v>-42.68590918494795</v>
       </c>
       <c r="F96">
-        <v>5.188466654676153</v>
+        <v>6.16297794814716</v>
       </c>
       <c r="G96">
-        <v>-8.457056205300439</v>
+        <v>-11.42658367721976</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.293971364612485</v>
       </c>
       <c r="E97">
-        <v>-43.28081309851072</v>
+        <v>-46.37950953172566</v>
       </c>
       <c r="F97">
-        <v>4.624141361518991</v>
+        <v>6.150443092607997</v>
       </c>
       <c r="G97">
-        <v>-7.867308582752382</v>
+        <v>-11.65206846606504</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.924339100469856</v>
       </c>
       <c r="E98">
-        <v>-45.38083664298004</v>
+        <v>-47.76041699493489</v>
       </c>
       <c r="F98">
-        <v>4.749701978965728</v>
+        <v>6.227810951294665</v>
       </c>
       <c r="G98">
-        <v>-8.740927686181369</v>
+        <v>-11.54559316403337</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.53755713460727</v>
       </c>
       <c r="E99">
-        <v>-48.89912890143391</v>
+        <v>-49.77215987948365</v>
       </c>
       <c r="F99">
-        <v>4.964722962445202</v>
+        <v>6.219727742178148</v>
       </c>
       <c r="G99">
-        <v>-7.992792716151946</v>
+        <v>-11.34823523204046</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.140969487653061</v>
       </c>
       <c r="E100">
-        <v>-50.07151504535464</v>
+        <v>-52.56228205598931</v>
       </c>
       <c r="F100">
-        <v>4.560265951089121</v>
+        <v>5.988440936377303</v>
       </c>
       <c r="G100">
-        <v>-8.245058523012858</v>
+        <v>-10.68141973453503</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.771861686556532</v>
       </c>
       <c r="E101">
-        <v>-53.31050799542512</v>
+        <v>-54.08084978516564</v>
       </c>
       <c r="F101">
-        <v>3.720944217754994</v>
+        <v>6.43647338659025</v>
       </c>
       <c r="G101">
-        <v>-8.580963448966971</v>
+        <v>-10.64148186915247</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.429687260907388</v>
       </c>
       <c r="E102">
-        <v>-54.26242091616733</v>
+        <v>-55.94767882016848</v>
       </c>
       <c r="F102">
-        <v>4.033722495173643</v>
+        <v>6.085156144123757</v>
       </c>
       <c r="G102">
-        <v>-8.577468967331766</v>
+        <v>-10.84130564941169</v>
       </c>
     </row>
   </sheetData>
